--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.42334154340994</v>
+        <v>4.131293000804114</v>
       </c>
       <c r="D2" t="n">
-        <v>6.252490423359415</v>
+        <v>1.016029693795905</v>
       </c>
       <c r="E2" t="n">
-        <v>4.079465369497202</v>
+        <v>0.6629131225432953</v>
       </c>
       <c r="F2" t="n">
-        <v>8.332939504942132</v>
+        <v>1.354102669553096</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.21414567022173</v>
+        <v>4.422298671411031</v>
       </c>
       <c r="D3" t="n">
-        <v>22.31703992113628</v>
+        <v>3.626518987184646</v>
       </c>
       <c r="E3" t="n">
-        <v>4.079465369497202</v>
+        <v>0.6629131225432953</v>
       </c>
       <c r="F3" t="n">
-        <v>8.332939504942132</v>
+        <v>1.354102669553096</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.88831417557376</v>
+        <v>5.669351053530736</v>
       </c>
       <c r="D4" t="n">
-        <v>27.93190067717003</v>
+        <v>4.538933860040131</v>
       </c>
       <c r="E4" t="n">
-        <v>4.079465369497202</v>
+        <v>0.6629131225432953</v>
       </c>
       <c r="F4" t="n">
-        <v>8.332939504942132</v>
+        <v>1.354102669553096</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.55555555555555</v>
+        <v>3.990277777777778</v>
       </c>
       <c r="D5" t="n">
-        <v>24.55555555555555</v>
+        <v>3.990277777777778</v>
       </c>
       <c r="E5" t="n">
-        <v>4.079465369497202</v>
+        <v>0.6629131225432953</v>
       </c>
       <c r="F5" t="n">
-        <v>8.332939504942132</v>
+        <v>1.354102669553096</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
